--- a/eoptolink/dist/20261025_新易盛模型_v0.2.xlsx
+++ b/eoptolink/dist/20261025_新易盛模型_v0.2.xlsx
@@ -4863,7 +4863,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5100,7 +5100,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5221,7 +5221,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5342,7 +5342,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5463,7 +5463,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5584,7 +5584,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
